--- a/nablarch_sample/アプリケーション方式設計書_4バッチ処理方式_4.2.常駐バッチ.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_4バッチ処理方式_4.2.常駐バッチ.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375520D2-A8E8-436B-89A3-44DAB9696A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8DCE13-0D00-4180-97F2-69541FF804F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.常駐バッチ" sheetId="4" r:id="rId1"/>
@@ -429,22 +429,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プロセスを起動しておき、一定間隔でバッチ処理を実行する処理方式。
-https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/batch/nablarch_batch/architecture.html#nablarch-batch-resident-batch</t>
-    <rPh sb="27" eb="31">
-      <t>ショリホウシキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>定期的にデータベース上のテーブルを監視し未処理のレコードを順次処理する処理方式。
-https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/messaging/db/index.html</t>
-    <rPh sb="35" eb="39">
-      <t>ショリホウシキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>新規プロジェクトではキュー方式を採用することがNablarchでは推奨されている。</t>
     <rPh sb="0" eb="2">
       <t>シンキ</t>
@@ -504,10 +488,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/mail.html#mail-send</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>※メール送信の実装に関する説明は下記解説書を参照。</t>
     <rPh sb="4" eb="6">
       <t>ソウシン</t>
@@ -764,6 +744,26 @@
   </si>
   <si>
     <t>ログ出力内容の詳細は「7.13.ログ」を参照。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プロセスを起動しておき、一定間隔でバッチ処理を実行する処理方式。
+https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/batch/nablarch_batch/architecture.html#nablarch-batch-resident-batch</t>
+    <rPh sb="27" eb="31">
+      <t>ショリホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>定期的にデータベース上のテーブルを監視し未処理のレコードを順次処理する処理方式。
+https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/messaging/db/index.html</t>
+    <rPh sb="35" eb="39">
+      <t>ショリホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/mail.html#mail-send</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -774,7 +774,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,6 +819,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -998,7 +1007,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1059,6 +1068,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1137,8 +1149,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1169,9 +1181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1209,9 +1221,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1244,26 +1256,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1296,26 +1291,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1493,144 +1471,144 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI542"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="4"/>
+    <col min="1" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="26"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="26" t="s">
+      <c r="R1" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="29"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="22"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="23"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="34"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="35" t="s">
+      <c r="R2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="38"/>
       <c r="Y2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="22"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="23"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="40"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="41"/>
       <c r="Y3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="22"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="23"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
@@ -1638,8 +1616,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"2."</f>
         <v>4.2.</v>
@@ -1648,8 +1626,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="15" t="str">
         <f>$C$7&amp;"1."</f>
         <v>4.2.1.</v>
@@ -1658,7 +1636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="str">
         <f>$D$9&amp;"1."</f>
@@ -1668,25 +1646,25 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E11" s="15"/>
       <c r="F11" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E12" s="15"/>
       <c r="F12" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="15" t="str">
         <f>$D$9&amp;"2."</f>
         <v>4.2.1.2.</v>
@@ -1695,115 +1673,115 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="15"/>
       <c r="F16" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E17" s="15"/>
     </row>
-    <row r="18" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E18" s="15"/>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="43" t="s">
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="44"/>
-      <c r="W18" s="44"/>
-      <c r="X18" s="44"/>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="44"/>
-      <c r="AB18" s="44"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="44"/>
-      <c r="AE18" s="45"/>
-    </row>
-    <row r="19" spans="5:31" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+      <c r="U18" s="45"/>
+      <c r="V18" s="45"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="45"/>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="45"/>
+      <c r="AA18" s="45"/>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="45"/>
+      <c r="AE18" s="46"/>
+    </row>
+    <row r="19" spans="5:31" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="15"/>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="42"/>
-      <c r="AE19" s="42"/>
-    </row>
-    <row r="20" spans="5:31" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="43"/>
+    </row>
+    <row r="20" spans="5:31" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E20" s="15"/>
-      <c r="F20" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
-      <c r="Z20" s="42"/>
-      <c r="AA20" s="42"/>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="42"/>
-    </row>
-    <row r="21" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F20" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="43"/>
+      <c r="Z20" s="43"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="43"/>
+    </row>
+    <row r="21" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E21" s="15"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
@@ -1814,72 +1792,72 @@
       <c r="L21" s="19"/>
       <c r="M21" s="18"/>
     </row>
-    <row r="22" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E22" s="15"/>
       <c r="F22" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M22" s="18"/>
     </row>
-    <row r="23" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E23" s="15"/>
       <c r="F23" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E25" s="15"/>
       <c r="F25" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E26" s="15"/>
       <c r="F26" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E27" s="15"/>
       <c r="F27" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="15"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="15"/>
-      <c r="F32" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F32" s="47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E33" s="15"/>
     </row>
-    <row r="34" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D35" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>4.2.2.</v>
@@ -1888,7 +1866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="15"/>
       <c r="E36" s="15" t="str">
         <f>$D$35&amp;"1."</f>
@@ -1899,18 +1877,18 @@
         <v>処理制御機能概要</v>
       </c>
     </row>
-    <row r="37" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F37" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F38" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E40" s="15" t="str">
         <f>$D$35&amp;"2."</f>
         <v>4.2.2.2.</v>
@@ -1919,43 +1897,43 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E41" s="15"/>
       <c r="F41" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E42" s="15"/>
       <c r="F42" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E43" s="15"/>
     </row>
-    <row r="44" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E44" s="15"/>
       <c r="F44" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E45" s="15"/>
       <c r="F45" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E46" s="15"/>
       <c r="F46" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E47" s="15"/>
     </row>
-    <row r="48" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E48" s="15" t="str">
         <f>$D$35&amp;"3."</f>
         <v>4.2.2.3.</v>
@@ -1964,39 +1942,39 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F50" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F51" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F52" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F54" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F55" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E57" s="15" t="str">
         <f>$D$35&amp;"4."</f>
         <v>4.2.2.4.</v>
@@ -2005,25 +1983,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="15"/>
       <c r="F58" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E59" s="15"/>
       <c r="F59" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D60" s="15"/>
     </row>
-    <row r="61" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D62" s="15" t="str">
         <f>$C$7&amp;"3."</f>
         <v>4.2.3.</v>
@@ -2032,31 +2010,31 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D63" s="15"/>
       <c r="E63" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D64" s="15"/>
       <c r="E64" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D65" s="15"/>
       <c r="E65" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="15"/>
     </row>
-    <row r="67" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D67" s="15"/>
     </row>
-    <row r="68" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D68" s="15" t="str">
         <f>$C$7&amp;"4."</f>
         <v>4.2.4.</v>
@@ -2065,152 +2043,152 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D69" s="15"/>
       <c r="E69" s="15" t="str">
         <f t="shared" ref="E69" si="0">$D$68&amp;"1."</f>
         <v>4.2.4.1.</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="15"/>
       <c r="F70" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F72" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G73" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G74" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F72" s="46" t="s">
+    <row r="75" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G75" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G72" s="4" t="s">
+    </row>
+    <row r="76" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F77" s="20" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="73" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G73" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G74" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G75" s="4" t="s">
+    <row r="78" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G78" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F77" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G78" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E80" s="15" t="str">
         <f>$D$68&amp;"2."</f>
         <v>4.2.4.2.</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F82" s="46" t="str">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F82" s="20" t="str">
         <f>$E$80&amp;"1."</f>
         <v>4.2.4.2.1.</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G83" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G84" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G85" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G83" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G84" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G85" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F87" s="46" t="str">
+    <row r="86" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F87" s="20" t="str">
         <f>$E$80&amp;"2."</f>
         <v>4.2.4.2.2.</v>
       </c>
       <c r="G87" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G88" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G89" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G90" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G91" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G88" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G89" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G90" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="91" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G91" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F93" s="46" t="str">
+    <row r="92" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F93" s="20" t="str">
         <f>$E$80&amp;"3."</f>
         <v>4.2.4.2.3.</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G94" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G95" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="96" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G96" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G96" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="97" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D98" s="15"/>
       <c r="E98" s="15" t="str">
         <f>$D$68&amp;"3."</f>
@@ -2220,498 +2198,498 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D99" s="15"/>
       <c r="F99" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D100" s="15"/>
       <c r="F100" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D101" s="15"/>
       <c r="F101" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D102" s="15"/>
       <c r="F102" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="15"/>
       <c r="F103" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D104" s="15"/>
     </row>
-    <row r="105" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D105" s="15"/>
       <c r="F105" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D106" s="15"/>
       <c r="F106" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="15"/>
       <c r="F107" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="15"/>
     </row>
-    <row r="109" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="15"/>
     </row>
-    <row r="110" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="15"/>
     </row>
-    <row r="111" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="F20:L20"/>

--- a/nablarch_sample/アプリケーション方式設計書_4バッチ処理方式_4.2.常駐バッチ.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_4バッチ処理方式_4.2.常駐バッチ.xlsx
@@ -1,22 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8DCE13-0D00-4180-97F2-69541FF804F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8FCD0F-F363-4756-9A0C-5D34CEBB21E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.常駐バッチ" sheetId="4" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'4.2.常駐バッチ'!$A$1:$AI$108</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'4.2.常駐バッチ'!$A$1:$AI$111</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'4.2.常駐バッチ'!$A$1:$AI$111</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'4.2.常駐バッチ'!$A$1:$AI$111</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'4.2.常駐バッチ'!$A$1:$AI$111</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1071,6 +1064,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1136,21 +1144,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1181,9 +1174,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1221,9 +1214,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1256,9 +1249,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1291,9 +1301,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1467,148 +1494,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI542"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="4"/>
+    <col min="1" max="16384" width="3.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="26"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="31"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="29"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="34"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="23"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="28"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="35"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="40"/>
       <c r="P2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="36" t="s">
+      <c r="R2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="38"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="43"/>
       <c r="Y2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="23"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="28"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="41"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="46"/>
       <c r="Y3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="23"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="37"/>
+      <c r="AF3" s="26"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="28"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
@@ -1616,8 +1643,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"2."</f>
         <v>4.2.</v>
@@ -1626,8 +1653,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D9" s="15" t="str">
         <f>$C$7&amp;"1."</f>
         <v>4.2.1.</v>
@@ -1636,7 +1663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="str">
         <f>$D$9&amp;"1."</f>
@@ -1646,25 +1673,25 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E11" s="15"/>
       <c r="F11" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E12" s="15"/>
       <c r="F12" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E15" s="15" t="str">
         <f>$D$9&amp;"2."</f>
         <v>4.2.1.2.</v>
@@ -1673,115 +1700,115 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E16" s="15"/>
       <c r="F16" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E17" s="15"/>
     </row>
-    <row r="18" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E18" s="15"/>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="44" t="s">
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="46"/>
-    </row>
-    <row r="19" spans="5:31" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
+      <c r="AE18" s="25"/>
+    </row>
+    <row r="19" spans="5:31" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E19" s="15"/>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43" t="s">
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="43"/>
-      <c r="AE19" s="43"/>
-    </row>
-    <row r="20" spans="5:31" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+    </row>
+    <row r="20" spans="5:31" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E20" s="15"/>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43" t="s">
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-    </row>
-    <row r="21" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
+      <c r="AE20" s="22"/>
+    </row>
+    <row r="21" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E21" s="15"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
@@ -1792,72 +1819,72 @@
       <c r="L21" s="19"/>
       <c r="M21" s="18"/>
     </row>
-    <row r="22" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E22" s="15"/>
       <c r="F22" s="4" t="s">
         <v>60</v>
       </c>
       <c r="M22" s="18"/>
     </row>
-    <row r="23" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E23" s="15"/>
       <c r="F23" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E25" s="15"/>
       <c r="F25" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E26" s="15"/>
       <c r="F26" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E27" s="15"/>
       <c r="F27" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E30" s="15"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E32" s="15"/>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="21" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E33" s="15"/>
     </row>
-    <row r="34" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D35" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>4.2.2.</v>
@@ -1866,7 +1893,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D36" s="15"/>
       <c r="E36" s="15" t="str">
         <f>$D$35&amp;"1."</f>
@@ -1877,18 +1904,18 @@
         <v>処理制御機能概要</v>
       </c>
     </row>
-    <row r="37" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F37" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F38" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E40" s="15" t="str">
         <f>$D$35&amp;"2."</f>
         <v>4.2.2.2.</v>
@@ -1897,43 +1924,43 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="15"/>
       <c r="F41" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="15"/>
       <c r="F42" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E43" s="15"/>
     </row>
-    <row r="44" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E44" s="15"/>
       <c r="F44" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E45" s="15"/>
       <c r="F45" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E46" s="15"/>
       <c r="F46" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E47" s="15"/>
     </row>
-    <row r="48" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E48" s="15" t="str">
         <f>$D$35&amp;"3."</f>
         <v>4.2.2.3.</v>
@@ -1942,39 +1969,39 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F49" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F50" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F51" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F54" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F55" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E57" s="15" t="str">
         <f>$D$35&amp;"4."</f>
         <v>4.2.2.4.</v>
@@ -1983,25 +2010,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E58" s="15"/>
       <c r="F58" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E59" s="15"/>
       <c r="F59" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D60" s="15"/>
     </row>
-    <row r="61" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D62" s="15" t="str">
         <f>$C$7&amp;"3."</f>
         <v>4.2.3.</v>
@@ -2010,31 +2037,31 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D63" s="15"/>
       <c r="E63" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D64" s="15"/>
       <c r="E64" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D65" s="15"/>
       <c r="E65" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D66" s="15"/>
     </row>
-    <row r="67" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D67" s="15"/>
     </row>
-    <row r="68" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D68" s="15" t="str">
         <f>$C$7&amp;"4."</f>
         <v>4.2.4.</v>
@@ -2043,7 +2070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D69" s="15"/>
       <c r="E69" s="15" t="str">
         <f t="shared" ref="E69" si="0">$D$68&amp;"1."</f>
@@ -2053,14 +2080,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E70" s="15"/>
       <c r="F70" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F72" s="20" t="s">
         <v>65</v>
       </c>
@@ -2068,23 +2095,23 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G73" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G74" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G75" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="20" t="s">
         <v>69</v>
       </c>
@@ -2092,13 +2119,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G78" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E80" s="15" t="str">
         <f>$D$68&amp;"2."</f>
         <v>4.2.4.2.</v>
@@ -2107,8 +2134,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F82" s="20" t="str">
         <f>$E$80&amp;"1."</f>
         <v>4.2.4.2.1.</v>
@@ -2117,23 +2144,23 @@
         <v>73</v>
       </c>
     </row>
-    <row r="83" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G83" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="84" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G84" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="85" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G85" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F87" s="20" t="str">
         <f>$E$80&amp;"2."</f>
         <v>4.2.4.2.2.</v>
@@ -2142,28 +2169,28 @@
         <v>77</v>
       </c>
     </row>
-    <row r="88" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G88" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G89" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="90" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G90" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="91" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G91" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F93" s="20" t="str">
         <f>$E$80&amp;"3."</f>
         <v>4.2.4.2.3.</v>
@@ -2172,23 +2199,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G94" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G95" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="6:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G96" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="97" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D98" s="15"/>
       <c r="E98" s="15" t="str">
         <f>$D$68&amp;"3."</f>
@@ -2198,506 +2225,500 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D99" s="15"/>
       <c r="F99" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D100" s="15"/>
       <c r="F100" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D101" s="15"/>
       <c r="F101" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D102" s="15"/>
       <c r="F102" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D103" s="15"/>
       <c r="F103" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D104" s="15"/>
     </row>
-    <row r="105" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D105" s="15"/>
       <c r="F105" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D106" s="15"/>
       <c r="F106" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D107" s="15"/>
       <c r="F107" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D108" s="15"/>
     </row>
-    <row r="109" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D109" s="15"/>
     </row>
-    <row r="110" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D110" s="15"/>
     </row>
-    <row r="111" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="M20:AE20"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="M18:AE18"/>
-    <mergeCell ref="M19:AE19"/>
-    <mergeCell ref="F19:L19"/>
     <mergeCell ref="AF3:AI3"/>
     <mergeCell ref="E1:O1"/>
     <mergeCell ref="R1:X1"/>
@@ -2709,6 +2730,12 @@
     <mergeCell ref="AF2:AI2"/>
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="M20:AE20"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="M18:AE18"/>
+    <mergeCell ref="M19:AE19"/>
+    <mergeCell ref="F19:L19"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
